--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Year_Num</t>
+  </si>
+  <si>
+    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -519,15 +522,15 @@
       <c r="F2">
         <v>24.3</v>
       </c>
-      <c r="H2">
-        <v>18.4</v>
-      </c>
       <c r="I2">
         <v>30.6</v>
       </c>
       <c r="K2">
         <v>18.4</v>
       </c>
+      <c r="M2">
+        <v>24.9</v>
+      </c>
       <c r="R2" s="2">
         <v>32174</v>
       </c>
@@ -548,8 +551,14 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>17.6</v>
+      <c r="D3">
+        <v>26.2</v>
+      </c>
+      <c r="E3">
+        <v>17.4</v>
+      </c>
+      <c r="F3">
+        <v>21.8</v>
       </c>
       <c r="I3">
         <v>23.9</v>
@@ -557,6 +566,9 @@
       <c r="K3">
         <v>17.6</v>
       </c>
+      <c r="M3">
+        <v>21.3</v>
+      </c>
       <c r="R3" s="2">
         <v>32175</v>
       </c>
@@ -577,8 +589,14 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>17.4</v>
+      <c r="D4">
+        <v>32.3</v>
+      </c>
+      <c r="E4">
+        <v>16.9</v>
+      </c>
+      <c r="F4">
+        <v>24.6</v>
       </c>
       <c r="I4">
         <v>29.5</v>
@@ -586,6 +604,9 @@
       <c r="K4">
         <v>17.5</v>
       </c>
+      <c r="M4">
+        <v>22.6</v>
+      </c>
       <c r="R4" s="2">
         <v>32176</v>
       </c>
@@ -615,18 +636,18 @@
       <c r="F5">
         <v>25.2</v>
       </c>
-      <c r="H5">
-        <v>20.3</v>
-      </c>
       <c r="I5">
         <v>20.1</v>
       </c>
       <c r="K5">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="L5">
         <v>19.5</v>
       </c>
+      <c r="M5">
+        <v>20.6</v>
+      </c>
       <c r="R5" s="2">
         <v>32177</v>
       </c>
@@ -656,15 +677,15 @@
       <c r="F6">
         <v>22.6</v>
       </c>
-      <c r="H6">
-        <v>18.9</v>
-      </c>
       <c r="I6">
         <v>25.8</v>
       </c>
       <c r="K6">
         <v>18.9</v>
       </c>
+      <c r="M6">
+        <v>21.4</v>
+      </c>
       <c r="R6" s="2">
         <v>32178</v>
       </c>
@@ -686,16 +707,16 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E7">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F7">
         <v>23.8</v>
       </c>
       <c r="M7">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="R7" s="2">
         <v>32179</v>
@@ -727,7 +748,7 @@
         <v>22.4</v>
       </c>
       <c r="M8">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="R8" s="2">
         <v>32180</v>
@@ -808,13 +829,13 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="E11">
         <v>18.6</v>
       </c>
       <c r="F11">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="M11">
         <v>20.9</v>
@@ -839,8 +860,14 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="H12">
-        <v>19.2</v>
+      <c r="D12">
+        <v>25.8</v>
+      </c>
+      <c r="O12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" t="s">
+        <v>20</v>
       </c>
       <c r="R12" s="2">
         <v>32184</v>
@@ -863,19 +890,13 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="E13">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="F13">
-        <v>24.1</v>
-      </c>
-      <c r="H13">
-        <v>18.3</v>
-      </c>
-      <c r="K13">
-        <v>18.2</v>
+        <v>24</v>
       </c>
       <c r="R13" s="2">
         <v>32185</v>
@@ -897,11 +918,14 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="H14">
-        <v>19.2</v>
-      </c>
-      <c r="K14">
-        <v>19.2</v>
+      <c r="D14">
+        <v>28.6</v>
+      </c>
+      <c r="E14">
+        <v>18.8</v>
+      </c>
+      <c r="F14">
+        <v>23.6</v>
       </c>
       <c r="R14" s="2">
         <v>32186</v>
@@ -923,8 +947,14 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="H15">
-        <v>19.4</v>
+      <c r="D15">
+        <v>28.4</v>
+      </c>
+      <c r="E15">
+        <v>18.4</v>
+      </c>
+      <c r="F15">
+        <v>23.4</v>
       </c>
       <c r="R15" s="2">
         <v>32187</v>
@@ -946,11 +976,14 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="H16">
-        <v>18</v>
-      </c>
-      <c r="K16">
-        <v>18</v>
+      <c r="D16">
+        <v>29.4</v>
+      </c>
+      <c r="E16">
+        <v>17.8</v>
+      </c>
+      <c r="F16">
+        <v>23.6</v>
       </c>
       <c r="R16" s="2">
         <v>32188</v>
@@ -972,9 +1005,18 @@
       <c r="C17">
         <v>16</v>
       </c>
+      <c r="D17">
+        <v>29.9</v>
+      </c>
+      <c r="E17">
+        <v>18.8</v>
+      </c>
       <c r="F17">
         <v>24.2</v>
       </c>
+      <c r="J17">
+        <v>25.3</v>
+      </c>
       <c r="R17" s="2">
         <v>32189</v>
       </c>
@@ -996,14 +1038,17 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>28.6</v>
+        <v>32.6</v>
       </c>
       <c r="E18">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="F18">
         <v>23.9</v>
       </c>
+      <c r="J18">
+        <v>20.9</v>
+      </c>
       <c r="R18" s="2">
         <v>32190</v>
       </c>
@@ -1033,6 +1078,9 @@
       <c r="F19">
         <v>22.4</v>
       </c>
+      <c r="J19">
+        <v>23.9</v>
+      </c>
       <c r="R19" s="2">
         <v>32191</v>
       </c>
@@ -1054,14 +1102,17 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>32.7</v>
+        <v>30.7</v>
       </c>
       <c r="E20">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="F20">
         <v>24.3</v>
       </c>
+      <c r="J20">
+        <v>21</v>
+      </c>
       <c r="R20" s="2">
         <v>32192</v>
       </c>
@@ -1083,14 +1134,17 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="E21">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F21">
         <v>24.2</v>
       </c>
+      <c r="J21">
+        <v>13.4</v>
+      </c>
       <c r="R21" s="2">
         <v>32193</v>
       </c>
@@ -1111,12 +1165,6 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="I22">
-        <v>29.9</v>
-      </c>
-      <c r="L22">
-        <v>24</v>
-      </c>
       <c r="M22">
         <v>25.8</v>
       </c>
@@ -1140,12 +1188,6 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="I23">
-        <v>28.9</v>
-      </c>
-      <c r="L23">
-        <v>27.8</v>
-      </c>
       <c r="M23">
         <v>27.4</v>
       </c>
@@ -1170,20 +1212,14 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E24">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F24">
         <v>25.8</v>
       </c>
-      <c r="I24">
-        <v>24.8</v>
-      </c>
-      <c r="L24">
-        <v>20.9</v>
-      </c>
       <c r="M24">
         <v>21.5</v>
       </c>
@@ -1207,12 +1243,6 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="I25">
-        <v>28</v>
-      </c>
-      <c r="L25">
-        <v>22.8</v>
-      </c>
       <c r="M25">
         <v>24.2</v>
       </c>
@@ -1236,12 +1266,6 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="I26">
-        <v>31.2</v>
-      </c>
-      <c r="L26">
-        <v>23</v>
-      </c>
       <c r="M26">
         <v>27</v>
       </c>
@@ -1294,6 +1318,9 @@
       <c r="F28">
         <v>25.4</v>
       </c>
+      <c r="M28">
+        <v>18.7</v>
+      </c>
       <c r="R28" s="2">
         <v>32200</v>
       </c>
@@ -1313,6 +1340,15 @@
       </c>
       <c r="C29">
         <v>28</v>
+      </c>
+      <c r="D29">
+        <v>31.8</v>
+      </c>
+      <c r="E29">
+        <v>19</v>
+      </c>
+      <c r="F29">
+        <v>25.4</v>
       </c>
       <c r="R29" s="2">
         <v>32201</v>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Year</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Year_Num</t>
-  </si>
-  <si>
-    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -522,12 +519,21 @@
       <c r="F2">
         <v>24.3</v>
       </c>
+      <c r="H2">
+        <v>18.4</v>
+      </c>
       <c r="I2">
         <v>30.6</v>
       </c>
+      <c r="J2">
+        <v>27.5</v>
+      </c>
       <c r="K2">
         <v>18.4</v>
       </c>
+      <c r="L2">
+        <v>23.8</v>
+      </c>
       <c r="M2">
         <v>24.9</v>
       </c>
@@ -560,12 +566,21 @@
       <c r="F3">
         <v>21.8</v>
       </c>
+      <c r="H3">
+        <v>17.6</v>
+      </c>
       <c r="I3">
         <v>23.9</v>
       </c>
+      <c r="J3">
+        <v>23.1</v>
+      </c>
       <c r="K3">
         <v>17.6</v>
       </c>
+      <c r="L3">
+        <v>21</v>
+      </c>
       <c r="M3">
         <v>21.3</v>
       </c>
@@ -590,20 +605,29 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="E4">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="F4">
         <v>24.6</v>
       </c>
+      <c r="H4">
+        <v>17.4</v>
+      </c>
       <c r="I4">
         <v>29.5</v>
       </c>
+      <c r="J4">
+        <v>27.2</v>
+      </c>
       <c r="K4">
         <v>17.5</v>
       </c>
+      <c r="L4">
+        <v>24.1</v>
+      </c>
       <c r="M4">
         <v>22.6</v>
       </c>
@@ -636,9 +660,15 @@
       <c r="F5">
         <v>25.2</v>
       </c>
+      <c r="H5">
+        <v>20.3</v>
+      </c>
       <c r="I5">
         <v>20.1</v>
       </c>
+      <c r="J5">
+        <v>21.4</v>
+      </c>
       <c r="K5">
         <v>20.2</v>
       </c>
@@ -677,12 +707,21 @@
       <c r="F6">
         <v>22.6</v>
       </c>
+      <c r="H6">
+        <v>18.9</v>
+      </c>
       <c r="I6">
         <v>25.8</v>
       </c>
+      <c r="J6">
+        <v>24.6</v>
+      </c>
       <c r="K6">
         <v>18.9</v>
       </c>
+      <c r="L6">
+        <v>22.3</v>
+      </c>
       <c r="M6">
         <v>21.4</v>
       </c>
@@ -707,14 +746,20 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="F7">
         <v>23.8</v>
       </c>
+      <c r="I7">
+        <v>28.4</v>
+      </c>
+      <c r="L7">
+        <v>23.8</v>
+      </c>
       <c r="M7">
         <v>22.9</v>
       </c>
@@ -739,16 +784,22 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="E8">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="F8">
         <v>22.4</v>
       </c>
+      <c r="I8">
+        <v>24.3</v>
+      </c>
+      <c r="L8">
+        <v>22</v>
+      </c>
       <c r="M8">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="R8" s="2">
         <v>32180</v>
@@ -770,9 +821,21 @@
       <c r="C9">
         <v>8</v>
       </c>
+      <c r="D9">
+        <v>26.8</v>
+      </c>
+      <c r="E9">
+        <v>18.5</v>
+      </c>
       <c r="F9">
         <v>22.7</v>
       </c>
+      <c r="I9">
+        <v>22.2</v>
+      </c>
+      <c r="L9">
+        <v>20.4</v>
+      </c>
       <c r="M9">
         <v>20</v>
       </c>
@@ -800,10 +863,16 @@
         <v>29.9</v>
       </c>
       <c r="E10">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F10">
-        <v>24.1</v>
+        <v>24.2</v>
+      </c>
+      <c r="I10">
+        <v>27.7</v>
+      </c>
+      <c r="L10">
+        <v>23.4</v>
       </c>
       <c r="M10">
         <v>22.8</v>
@@ -837,6 +906,12 @@
       <c r="F11">
         <v>23.5</v>
       </c>
+      <c r="I11">
+        <v>26.6</v>
+      </c>
+      <c r="L11">
+        <v>22.9</v>
+      </c>
       <c r="M11">
         <v>20.9</v>
       </c>
@@ -861,13 +936,19 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>25.8</v>
-      </c>
-      <c r="O12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P12" t="s">
-        <v>20</v>
+        <v>25.9</v>
+      </c>
+      <c r="E12">
+        <v>18.7</v>
+      </c>
+      <c r="F12">
+        <v>22.3</v>
+      </c>
+      <c r="H12">
+        <v>19.2</v>
+      </c>
+      <c r="J12">
+        <v>21.8</v>
       </c>
       <c r="R12" s="2">
         <v>32184</v>
@@ -890,13 +971,25 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="E13">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>24.1</v>
+      </c>
+      <c r="H13">
+        <v>18.3</v>
+      </c>
+      <c r="J13">
+        <v>20.2</v>
+      </c>
+      <c r="K13">
+        <v>18.2</v>
+      </c>
+      <c r="M13">
+        <v>19.9</v>
       </c>
       <c r="R13" s="2">
         <v>32185</v>
@@ -919,13 +1012,22 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="E14">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="F14">
-        <v>23.6</v>
+        <v>23.7</v>
+      </c>
+      <c r="H14">
+        <v>19.2</v>
+      </c>
+      <c r="J14">
+        <v>22.8</v>
+      </c>
+      <c r="K14">
+        <v>19.2</v>
       </c>
       <c r="R14" s="2">
         <v>32186</v>
@@ -951,10 +1053,19 @@
         <v>28.4</v>
       </c>
       <c r="E15">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="F15">
-        <v>23.4</v>
+        <v>23.1</v>
+      </c>
+      <c r="H15">
+        <v>19.4</v>
+      </c>
+      <c r="J15">
+        <v>19.5</v>
+      </c>
+      <c r="M15">
+        <v>19.1</v>
       </c>
       <c r="R15" s="2">
         <v>32187</v>
@@ -977,13 +1088,22 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="E16">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="F16">
-        <v>23.6</v>
+        <v>23.3</v>
+      </c>
+      <c r="H16">
+        <v>18</v>
+      </c>
+      <c r="J16">
+        <v>24.6</v>
+      </c>
+      <c r="K16">
+        <v>18</v>
       </c>
       <c r="R16" s="2">
         <v>32188</v>
@@ -1006,16 +1126,19 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="E17">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="F17">
-        <v>24.2</v>
-      </c>
-      <c r="J17">
-        <v>25.3</v>
+        <v>24.3</v>
+      </c>
+      <c r="H17">
+        <v>19.1</v>
+      </c>
+      <c r="K17">
+        <v>19.1</v>
       </c>
       <c r="R17" s="2">
         <v>32189</v>
@@ -1038,16 +1161,16 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>32.6</v>
+        <v>28.6</v>
       </c>
       <c r="E18">
-        <v>15.2</v>
+        <v>19.2</v>
       </c>
       <c r="F18">
         <v>23.9</v>
       </c>
-      <c r="J18">
-        <v>20.9</v>
+      <c r="H18">
+        <v>19.6</v>
       </c>
       <c r="R18" s="2">
         <v>32190</v>
@@ -1070,16 +1193,16 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="E19">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="F19">
         <v>22.4</v>
       </c>
-      <c r="J19">
-        <v>23.9</v>
+      <c r="H19">
+        <v>18</v>
       </c>
       <c r="R19" s="2">
         <v>32191</v>
@@ -1102,16 +1225,16 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>30.7</v>
+        <v>32.7</v>
       </c>
       <c r="E20">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="F20">
         <v>24.3</v>
       </c>
-      <c r="J20">
-        <v>21</v>
+      <c r="H20">
+        <v>16.8</v>
       </c>
       <c r="R20" s="2">
         <v>32192</v>
@@ -1134,16 +1257,16 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="E21">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F21">
-        <v>24.2</v>
-      </c>
-      <c r="J21">
-        <v>13.4</v>
+        <v>24.3</v>
+      </c>
+      <c r="H21">
+        <v>18.2</v>
       </c>
       <c r="R21" s="2">
         <v>32193</v>
@@ -1165,6 +1288,15 @@
       <c r="C22">
         <v>21</v>
       </c>
+      <c r="G22">
+        <v>22.5</v>
+      </c>
+      <c r="I22">
+        <v>29.9</v>
+      </c>
+      <c r="J22">
+        <v>22.2</v>
+      </c>
       <c r="M22">
         <v>25.8</v>
       </c>
@@ -1188,6 +1320,24 @@
       <c r="C23">
         <v>22</v>
       </c>
+      <c r="D23">
+        <v>32.6</v>
+      </c>
+      <c r="E23">
+        <v>18</v>
+      </c>
+      <c r="F23">
+        <v>25.3</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>28.9</v>
+      </c>
+      <c r="J23">
+        <v>22</v>
+      </c>
       <c r="M23">
         <v>27.4</v>
       </c>
@@ -1215,11 +1365,20 @@
         <v>32.2</v>
       </c>
       <c r="E24">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F24">
         <v>25.8</v>
       </c>
+      <c r="G24">
+        <v>13.5</v>
+      </c>
+      <c r="I24">
+        <v>24.8</v>
+      </c>
+      <c r="J24">
+        <v>20</v>
+      </c>
       <c r="M24">
         <v>21.5</v>
       </c>
@@ -1243,6 +1402,24 @@
       <c r="C25">
         <v>24</v>
       </c>
+      <c r="D25">
+        <v>30.4</v>
+      </c>
+      <c r="E25">
+        <v>18.4</v>
+      </c>
+      <c r="F25">
+        <v>24.4</v>
+      </c>
+      <c r="G25">
+        <v>1.6</v>
+      </c>
+      <c r="I25">
+        <v>28</v>
+      </c>
+      <c r="J25">
+        <v>22</v>
+      </c>
       <c r="M25">
         <v>24.2</v>
       </c>
@@ -1266,6 +1443,15 @@
       <c r="C26">
         <v>25</v>
       </c>
+      <c r="G26">
+        <v>11.5</v>
+      </c>
+      <c r="I26">
+        <v>31.2</v>
+      </c>
+      <c r="J26">
+        <v>23.9</v>
+      </c>
       <c r="M26">
         <v>27</v>
       </c>
@@ -1289,6 +1475,9 @@
       <c r="C27">
         <v>26</v>
       </c>
+      <c r="G27">
+        <v>6.2</v>
+      </c>
       <c r="R27" s="2">
         <v>32199</v>
       </c>
@@ -1318,8 +1507,8 @@
       <c r="F28">
         <v>25.4</v>
       </c>
-      <c r="M28">
-        <v>18.7</v>
+      <c r="G28">
+        <v>0</v>
       </c>
       <c r="R28" s="2">
         <v>32200</v>
@@ -1350,6 +1539,9 @@
       <c r="F29">
         <v>25.4</v>
       </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
       <c r="R29" s="2">
         <v>32201</v>
       </c>
@@ -1369,6 +1561,9 @@
       </c>
       <c r="C30">
         <v>29</v>
+      </c>
+      <c r="G30">
+        <v>1.5</v>
       </c>
       <c r="R30" s="2">
         <v>32202</v>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Year_Num</t>
+  </si>
+  <si>
+    <t>Condition 1</t>
   </si>
 </sst>
 </file>
@@ -531,9 +534,6 @@
       <c r="K2">
         <v>18.4</v>
       </c>
-      <c r="L2">
-        <v>23.8</v>
-      </c>
       <c r="M2">
         <v>24.9</v>
       </c>
@@ -578,9 +578,6 @@
       <c r="K3">
         <v>17.6</v>
       </c>
-      <c r="L3">
-        <v>21</v>
-      </c>
       <c r="M3">
         <v>21.3</v>
       </c>
@@ -625,9 +622,6 @@
       <c r="K4">
         <v>17.5</v>
       </c>
-      <c r="L4">
-        <v>24.1</v>
-      </c>
       <c r="M4">
         <v>22.6</v>
       </c>
@@ -719,9 +713,6 @@
       <c r="K6">
         <v>18.9</v>
       </c>
-      <c r="L6">
-        <v>22.3</v>
-      </c>
       <c r="M6">
         <v>21.4</v>
       </c>
@@ -746,10 +737,10 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E7">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F7">
         <v>23.8</v>
@@ -757,9 +748,6 @@
       <c r="I7">
         <v>28.4</v>
       </c>
-      <c r="L7">
-        <v>23.8</v>
-      </c>
       <c r="M7">
         <v>22.9</v>
       </c>
@@ -784,19 +772,16 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="E8">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="F8">
         <v>22.4</v>
       </c>
       <c r="I8">
-        <v>24.3</v>
-      </c>
-      <c r="L8">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="M8">
         <v>21.1</v>
@@ -825,7 +810,7 @@
         <v>26.8</v>
       </c>
       <c r="E9">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="F9">
         <v>22.7</v>
@@ -833,9 +818,6 @@
       <c r="I9">
         <v>22.2</v>
       </c>
-      <c r="L9">
-        <v>20.4</v>
-      </c>
       <c r="M9">
         <v>20</v>
       </c>
@@ -863,17 +845,14 @@
         <v>29.9</v>
       </c>
       <c r="E10">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="F10">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="I10">
         <v>27.7</v>
       </c>
-      <c r="L10">
-        <v>23.4</v>
-      </c>
       <c r="M10">
         <v>22.8</v>
       </c>
@@ -909,9 +888,6 @@
       <c r="I11">
         <v>26.6</v>
       </c>
-      <c r="L11">
-        <v>22.9</v>
-      </c>
       <c r="M11">
         <v>20.9</v>
       </c>
@@ -936,19 +912,25 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>25.9</v>
-      </c>
-      <c r="E12">
-        <v>18.7</v>
-      </c>
-      <c r="F12">
-        <v>22.3</v>
+        <v>25.8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
       </c>
       <c r="H12">
         <v>19.2</v>
       </c>
-      <c r="J12">
-        <v>21.8</v>
+      <c r="K12">
+        <v>19.6</v>
+      </c>
+      <c r="L12">
+        <v>23.2</v>
+      </c>
+      <c r="O12" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" t="s">
+        <v>20</v>
       </c>
       <c r="R12" s="2">
         <v>32184</v>
@@ -979,17 +961,20 @@
       <c r="F13">
         <v>24.1</v>
       </c>
+      <c r="G13">
+        <v>27.9</v>
+      </c>
       <c r="H13">
         <v>18.3</v>
       </c>
-      <c r="J13">
-        <v>20.2</v>
+      <c r="I13">
+        <v>19.9</v>
       </c>
       <c r="K13">
         <v>18.2</v>
       </c>
-      <c r="M13">
-        <v>19.9</v>
+      <c r="L13">
+        <v>19.8</v>
       </c>
       <c r="R13" s="2">
         <v>32185</v>
@@ -1020,15 +1005,18 @@
       <c r="F14">
         <v>23.7</v>
       </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
       <c r="H14">
         <v>19.2</v>
       </c>
-      <c r="J14">
-        <v>22.8</v>
-      </c>
       <c r="K14">
         <v>19.2</v>
       </c>
+      <c r="L14">
+        <v>21.9</v>
+      </c>
       <c r="R14" s="2">
         <v>32186</v>
       </c>
@@ -1053,18 +1041,24 @@
         <v>28.4</v>
       </c>
       <c r="E15">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="F15">
-        <v>23.1</v>
+        <v>23.4</v>
+      </c>
+      <c r="G15">
+        <v>3.8</v>
       </c>
       <c r="H15">
         <v>19.4</v>
       </c>
-      <c r="J15">
-        <v>19.5</v>
-      </c>
-      <c r="M15">
+      <c r="I15">
+        <v>19.2</v>
+      </c>
+      <c r="K15">
+        <v>18.4</v>
+      </c>
+      <c r="L15">
         <v>19.1</v>
       </c>
       <c r="R15" s="2">
@@ -1096,15 +1090,18 @@
       <c r="F16">
         <v>23.3</v>
       </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
       <c r="H16">
         <v>18</v>
       </c>
-      <c r="J16">
-        <v>24.6</v>
-      </c>
       <c r="K16">
         <v>18</v>
       </c>
+      <c r="L16">
+        <v>23.1</v>
+      </c>
       <c r="R16" s="2">
         <v>32188</v>
       </c>
@@ -1132,13 +1129,7 @@
         <v>18.7</v>
       </c>
       <c r="F17">
-        <v>24.3</v>
-      </c>
-      <c r="H17">
-        <v>19.1</v>
-      </c>
-      <c r="K17">
-        <v>19.1</v>
+        <v>24.2</v>
       </c>
       <c r="R17" s="2">
         <v>32189</v>
@@ -1169,9 +1160,6 @@
       <c r="F18">
         <v>23.9</v>
       </c>
-      <c r="H18">
-        <v>19.6</v>
-      </c>
       <c r="R18" s="2">
         <v>32190</v>
       </c>
@@ -1201,9 +1189,6 @@
       <c r="F19">
         <v>22.4</v>
       </c>
-      <c r="H19">
-        <v>18</v>
-      </c>
       <c r="R19" s="2">
         <v>32191</v>
       </c>
@@ -1233,9 +1218,6 @@
       <c r="F20">
         <v>24.3</v>
       </c>
-      <c r="H20">
-        <v>16.8</v>
-      </c>
       <c r="R20" s="2">
         <v>32192</v>
       </c>
@@ -1265,9 +1247,6 @@
       <c r="F21">
         <v>24.3</v>
       </c>
-      <c r="H21">
-        <v>18.2</v>
-      </c>
       <c r="R21" s="2">
         <v>32193</v>
       </c>
@@ -1288,6 +1267,15 @@
       <c r="C22">
         <v>21</v>
       </c>
+      <c r="D22">
+        <v>32.8</v>
+      </c>
+      <c r="E22">
+        <v>18.1</v>
+      </c>
+      <c r="F22">
+        <v>25.6</v>
+      </c>
       <c r="G22">
         <v>22.5</v>
       </c>
@@ -1295,7 +1283,10 @@
         <v>29.9</v>
       </c>
       <c r="J22">
-        <v>22.2</v>
+        <v>22.1</v>
+      </c>
+      <c r="L22">
+        <v>24</v>
       </c>
       <c r="M22">
         <v>25.8</v>
@@ -1338,6 +1329,9 @@
       <c r="J23">
         <v>22</v>
       </c>
+      <c r="L23">
+        <v>24.8</v>
+      </c>
       <c r="M23">
         <v>27.4</v>
       </c>
@@ -1379,6 +1373,9 @@
       <c r="J24">
         <v>20</v>
       </c>
+      <c r="L24">
+        <v>20.9</v>
+      </c>
       <c r="M24">
         <v>21.5</v>
       </c>
@@ -1420,6 +1417,9 @@
       <c r="J25">
         <v>22</v>
       </c>
+      <c r="L25">
+        <v>22.8</v>
+      </c>
       <c r="M25">
         <v>24.2</v>
       </c>
@@ -1443,6 +1443,15 @@
       <c r="C26">
         <v>25</v>
       </c>
+      <c r="D26">
+        <v>33.6</v>
+      </c>
+      <c r="E26">
+        <v>18</v>
+      </c>
+      <c r="F26">
+        <v>25.8</v>
+      </c>
       <c r="G26">
         <v>11.5</v>
       </c>
@@ -1451,6 +1460,9 @@
       </c>
       <c r="J26">
         <v>23.9</v>
+      </c>
+      <c r="L26">
+        <v>25</v>
       </c>
       <c r="M26">
         <v>27</v>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -534,6 +534,9 @@
       <c r="K2">
         <v>18.4</v>
       </c>
+      <c r="L2">
+        <v>23.8</v>
+      </c>
       <c r="M2">
         <v>24.9</v>
       </c>
@@ -578,6 +581,9 @@
       <c r="K3">
         <v>17.6</v>
       </c>
+      <c r="L3">
+        <v>21</v>
+      </c>
       <c r="M3">
         <v>21.3</v>
       </c>
@@ -622,6 +628,9 @@
       <c r="K4">
         <v>17.5</v>
       </c>
+      <c r="L4">
+        <v>24.1</v>
+      </c>
       <c r="M4">
         <v>22.6</v>
       </c>
@@ -713,6 +722,9 @@
       <c r="K6">
         <v>18.9</v>
       </c>
+      <c r="L6">
+        <v>22.3</v>
+      </c>
       <c r="M6">
         <v>21.4</v>
       </c>
@@ -748,6 +760,9 @@
       <c r="I7">
         <v>28.4</v>
       </c>
+      <c r="K7">
+        <v>19.3</v>
+      </c>
       <c r="M7">
         <v>22.9</v>
       </c>
@@ -781,7 +796,10 @@
         <v>22.4</v>
       </c>
       <c r="I8">
-        <v>24.2</v>
+        <v>24.3</v>
+      </c>
+      <c r="K8">
+        <v>18.8</v>
       </c>
       <c r="M8">
         <v>21.1</v>
@@ -818,6 +836,9 @@
       <c r="I9">
         <v>22.2</v>
       </c>
+      <c r="K9">
+        <v>18.9</v>
+      </c>
       <c r="M9">
         <v>20</v>
       </c>
@@ -853,6 +874,9 @@
       <c r="I10">
         <v>27.7</v>
       </c>
+      <c r="K10">
+        <v>18.7</v>
+      </c>
       <c r="M10">
         <v>22.8</v>
       </c>
@@ -888,6 +912,9 @@
       <c r="I11">
         <v>26.6</v>
       </c>
+      <c r="K11">
+        <v>18.9</v>
+      </c>
       <c r="M11">
         <v>20.9</v>
       </c>
@@ -912,26 +939,17 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>25.8</v>
+        <v>24.8</v>
+      </c>
+      <c r="E12">
+        <v>13.5</v>
+      </c>
+      <c r="F12">
+        <v>19.2</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="H12">
-        <v>19.2</v>
-      </c>
-      <c r="K12">
-        <v>19.6</v>
-      </c>
-      <c r="L12">
-        <v>23.2</v>
-      </c>
-      <c r="O12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P12" t="s">
-        <v>20</v>
-      </c>
       <c r="R12" s="2">
         <v>32184</v>
       </c>
@@ -964,18 +982,6 @@
       <c r="G13">
         <v>27.9</v>
       </c>
-      <c r="H13">
-        <v>18.3</v>
-      </c>
-      <c r="I13">
-        <v>19.9</v>
-      </c>
-      <c r="K13">
-        <v>18.2</v>
-      </c>
-      <c r="L13">
-        <v>19.8</v>
-      </c>
       <c r="R13" s="2">
         <v>32185</v>
       </c>
@@ -1008,15 +1014,6 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="H14">
-        <v>19.2</v>
-      </c>
-      <c r="K14">
-        <v>19.2</v>
-      </c>
-      <c r="L14">
-        <v>21.9</v>
-      </c>
       <c r="R14" s="2">
         <v>32186</v>
       </c>
@@ -1049,18 +1046,6 @@
       <c r="G15">
         <v>3.8</v>
       </c>
-      <c r="H15">
-        <v>19.4</v>
-      </c>
-      <c r="I15">
-        <v>19.2</v>
-      </c>
-      <c r="K15">
-        <v>18.4</v>
-      </c>
-      <c r="L15">
-        <v>19.1</v>
-      </c>
       <c r="R15" s="2">
         <v>32187</v>
       </c>
@@ -1082,26 +1067,17 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
       <c r="E16">
         <v>17</v>
       </c>
       <c r="F16">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
-      <c r="H16">
-        <v>18</v>
-      </c>
-      <c r="K16">
-        <v>18</v>
-      </c>
-      <c r="L16">
-        <v>23.1</v>
-      </c>
       <c r="R16" s="2">
         <v>32188</v>
       </c>
@@ -1129,7 +1105,13 @@
         <v>18.7</v>
       </c>
       <c r="F17">
-        <v>24.2</v>
+        <v>24.3</v>
+      </c>
+      <c r="H17">
+        <v>19.1</v>
+      </c>
+      <c r="K17">
+        <v>19.1</v>
       </c>
       <c r="R17" s="2">
         <v>32189</v>
@@ -1160,6 +1142,9 @@
       <c r="F18">
         <v>23.9</v>
       </c>
+      <c r="H18">
+        <v>19.6</v>
+      </c>
       <c r="R18" s="2">
         <v>32190</v>
       </c>
@@ -1189,6 +1174,12 @@
       <c r="F19">
         <v>22.4</v>
       </c>
+      <c r="H19">
+        <v>18</v>
+      </c>
+      <c r="K19">
+        <v>18</v>
+      </c>
       <c r="R19" s="2">
         <v>32191</v>
       </c>
@@ -1218,6 +1209,9 @@
       <c r="F20">
         <v>24.3</v>
       </c>
+      <c r="H20">
+        <v>16.8</v>
+      </c>
       <c r="R20" s="2">
         <v>32192</v>
       </c>
@@ -1247,6 +1241,9 @@
       <c r="F21">
         <v>24.3</v>
       </c>
+      <c r="H21">
+        <v>18.2</v>
+      </c>
       <c r="R21" s="2">
         <v>32193</v>
       </c>
@@ -1267,27 +1264,12 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22">
-        <v>32.8</v>
-      </c>
-      <c r="E22">
-        <v>18.1</v>
-      </c>
-      <c r="F22">
-        <v>25.6</v>
-      </c>
       <c r="G22">
         <v>22.5</v>
       </c>
       <c r="I22">
         <v>29.9</v>
       </c>
-      <c r="J22">
-        <v>22.1</v>
-      </c>
-      <c r="L22">
-        <v>24</v>
-      </c>
       <c r="M22">
         <v>25.8</v>
       </c>
@@ -1323,15 +1305,12 @@
       <c r="G23">
         <v>0</v>
       </c>
+      <c r="H23">
+        <v>18.8</v>
+      </c>
       <c r="I23">
         <v>28.9</v>
       </c>
-      <c r="J23">
-        <v>22</v>
-      </c>
-      <c r="L23">
-        <v>24.8</v>
-      </c>
       <c r="M23">
         <v>27.4</v>
       </c>
@@ -1367,15 +1346,12 @@
       <c r="G24">
         <v>13.5</v>
       </c>
+      <c r="H24">
+        <v>19.7</v>
+      </c>
       <c r="I24">
         <v>24.8</v>
       </c>
-      <c r="J24">
-        <v>20</v>
-      </c>
-      <c r="L24">
-        <v>20.9</v>
-      </c>
       <c r="M24">
         <v>21.5</v>
       </c>
@@ -1402,27 +1378,24 @@
       <c r="D25">
         <v>30.4</v>
       </c>
-      <c r="E25">
-        <v>18.4</v>
-      </c>
       <c r="F25">
-        <v>24.4</v>
+        <v>27.4</v>
       </c>
       <c r="G25">
         <v>1.6</v>
       </c>
+      <c r="H25">
+        <v>19</v>
+      </c>
       <c r="I25">
         <v>28</v>
       </c>
-      <c r="J25">
-        <v>22</v>
-      </c>
-      <c r="L25">
-        <v>22.8</v>
-      </c>
       <c r="M25">
         <v>24.2</v>
       </c>
+      <c r="O25" t="s">
+        <v>20</v>
+      </c>
       <c r="R25" s="2">
         <v>32197</v>
       </c>
@@ -1455,15 +1428,12 @@
       <c r="G26">
         <v>11.5</v>
       </c>
+      <c r="H26">
+        <v>18.7</v>
+      </c>
       <c r="I26">
         <v>31.2</v>
       </c>
-      <c r="J26">
-        <v>23.9</v>
-      </c>
-      <c r="L26">
-        <v>25</v>
-      </c>
       <c r="M26">
         <v>27</v>
       </c>
@@ -1490,6 +1460,12 @@
       <c r="G27">
         <v>6.2</v>
       </c>
+      <c r="I27">
+        <v>26.4</v>
+      </c>
+      <c r="K27">
+        <v>19</v>
+      </c>
       <c r="R27" s="2">
         <v>32199</v>
       </c>
@@ -1522,6 +1498,12 @@
       <c r="G28">
         <v>0</v>
       </c>
+      <c r="I28">
+        <v>31.2</v>
+      </c>
+      <c r="K28">
+        <v>18.8</v>
+      </c>
       <c r="R28" s="2">
         <v>32200</v>
       </c>
@@ -1554,6 +1536,12 @@
       <c r="G29">
         <v>0</v>
       </c>
+      <c r="I29">
+        <v>24.1</v>
+      </c>
+      <c r="K29">
+        <v>20</v>
+      </c>
       <c r="R29" s="2">
         <v>32201</v>
       </c>
@@ -1576,6 +1564,12 @@
       </c>
       <c r="G30">
         <v>1.5</v>
+      </c>
+      <c r="I30">
+        <v>25</v>
+      </c>
+      <c r="K30">
+        <v>19.3</v>
       </c>
       <c r="R30" s="2">
         <v>32202</v>

--- a/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/508/Daily_temperature_and_precipitation_station_508.xlsx
@@ -836,6 +836,9 @@
       <c r="I9">
         <v>22.2</v>
       </c>
+      <c r="J9">
+        <v>21.2</v>
+      </c>
       <c r="K9">
         <v>18.9</v>
       </c>
